--- a/docs/最新版/04_経理関係/請求・P&L管理.xlsx
+++ b/docs/最新版/04_経理関係/請求・P&L管理.xlsx
@@ -53,7 +53,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -63,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="003D2200"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -142,25 +137,27 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +166,10 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -181,26 +178,16 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -582,14 +569,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ぺいほーむ 請求・P&amp;L 管理</t>
+          <t>ぺいほーむ 請求・P&amp;L 管理 (全員同一料金)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01 MVPリリース以降の経理管理。各シートの更新タイミングを守って月次で回す</t>
+          <t>全員同一料金モデル、成果報酬 Phase 3〜</t>
         </is>
       </c>
     </row>
@@ -623,7 +610,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>毎月の請求明細 (工務店 x 項目 x 金額)</t>
+          <t>毎月の請求明細</t>
         </is>
       </c>
     </row>
@@ -691,7 +678,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>人件費・SaaS・家賃などの固定費</t>
+          <t>人件費・SaaS・家賃等</t>
         </is>
       </c>
     </row>
@@ -811,15 +798,17 @@
       <c r="B5" s="4" t="inlineStr"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>(10社のうちのA社)</t>
+          <t>(見学会予約発生の工務店)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>成果報酬 1.5%</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+          <t>見学会予約 ¥50,000/件</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>50000</v>
+      </c>
       <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
@@ -840,21 +829,19 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>(10社のうちのB社)</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>成果報酬 1.5%</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
+          <t>見学会予約 ¥50,000/件</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>50000</v>
+      </c>
       <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
@@ -873,51 +860,53 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>見学会予約 (10社無料)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="n">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>撮影プラン ¥150,000/本</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>税別</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>無料</t>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>未請求</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr"/>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>見学会予約 ¥25,000/件</t>
+          <t>月額掲載 ベーシック ¥30,000/月</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>0</v>
@@ -939,18 +928,18 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr"/>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>撮影プラン ¥75,000/本</t>
+          <t>月額掲載 プロ ¥80,000/月</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>75000</v>
+        <v>80000</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>0</v>
@@ -970,53 +959,53 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>月額掲載ベーシック(10社初年度無料)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>成果報酬 3% (無料相談/AI診断/会員成約)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>無料</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>税別</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>未請求</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>月額掲載ベーシック(新規)</t>
+          <t>SaaS ライト ¥50,000/月</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>0</v>
@@ -1045,11 +1034,11 @@
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>SaaSライト ¥25,000/月 (10社)</t>
+          <t>SaaS プロ ¥150,000/月</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>25000</v>
+        <v>150000</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0</v>
@@ -1687,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1709,76 +1698,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>③ 月次 P&amp;L (12ヶ月計画)</t>
+          <t>③ 月次 P&amp;L (12ヶ月計画、全員同一料金)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>フェーズ別収益モデル.xlsx と連動。毎月実績を記入</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>P5</t>
+          <t>毎月実績を記入</t>
         </is>
       </c>
     </row>
@@ -1855,546 +1782,550 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>【売上】見学会予約</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr"/>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>¥500,000</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>¥750,000</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>¥1,000,000</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>¥1,250,000</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>¥1,500,000</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>¥1,750,000</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>¥2,000,000</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>¥2,250,000</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>¥2,500,000</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>¥2,750,000</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>¥3,000,000</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>¥3,250,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>【売上】撮影プラン</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>¥50,000</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>¥125,000</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>¥175,000</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>¥225,000</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>¥275,000</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>¥325,000</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>¥375,000</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>¥425,000</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>¥475,000</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>¥150,000</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>¥300,000</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>¥450,000</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>¥450,000</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>¥600,000</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>¥600,000</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>¥750,000</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>¥750,000</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>¥900,000</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>¥900,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>【売上】月額掲載</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>¥90,000</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>¥150,000</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>¥240,000</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>¥300,000</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>¥360,000</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>¥390,000</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>¥450,000</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>¥510,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>【売上】成果報酬</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>¥900,000</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>¥1,800,000</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>¥1,800,000</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>¥2,700,000</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>¥2,700,000</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>¥3,600,000</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>¥3,600,000</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>¥4,500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>【売上】SaaS</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>¥100,000</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>¥200,000</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>¥450,000</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>¥550,000</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>¥800,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>売上合計</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>¥500,000</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>¥550,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>【売上】成果報酬</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>¥125,000</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>¥125,000</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>¥125,000</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>¥250,000</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>¥250,000</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>¥375,000</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>¥500,000</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>¥500,000</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>¥625,000</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>¥750,000</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>¥750,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>【売上】撮影プラン</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>¥75,000</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>¥150,000</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>¥225,000</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>¥225,000</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>¥300,000</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>¥300,000</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>¥375,000</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>¥375,000</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>¥450,000</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>¥450,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>【売上】月額掲載</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>¥30,000</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>¥90,000</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>¥180,000</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>¥240,000</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>¥270,000</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>¥300,000</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>¥360,000</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>¥390,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>【売上】SaaS</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>¥75,000</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>¥150,000</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>¥225,000</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>¥300,000</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>¥375,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>売上合計</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>¥175,000</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>¥325,000</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>¥450,000</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>¥730,000</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>¥840,000</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>¥1,180,000</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>¥1,490,000</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>¥1,720,000</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>¥2,000,000</t>
-        </is>
-      </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>¥2,360,000</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>¥2,515,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>【原価】見学会予約 (10%)</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr"/>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>¥5,000</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>¥12,500</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>¥17,500</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>¥22,500</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>¥27,500</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>¥32,500</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>¥37,500</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>¥42,500</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>¥47,500</t>
-        </is>
-      </c>
-      <c r="M12" s="12" t="inlineStr">
-        <is>
-          <t>¥50,000</t>
-        </is>
-      </c>
-      <c r="N12" s="12" t="inlineStr">
-        <is>
-          <t>¥55,000</t>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>¥1,150,000</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>¥1,550,000</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>¥2,940,000</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>¥4,150,000</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>¥4,640,000</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>¥5,950,000</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>¥6,510,000</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>¥7,940,000</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>¥8,500,000</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>¥9,960,000</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>【原価】成果報酬 (2%)</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr"/>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>¥2,500</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>¥2,500</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>¥2,500</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>¥5,000</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>¥5,000</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>¥7,500</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>¥10,000</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>¥10,000</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>¥12,500</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="inlineStr">
-        <is>
-          <t>¥15,000</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>¥15,000</t>
+          <t>【原価】見学会予約 (10%)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>¥50,000</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>¥75,000</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>¥100,000</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>¥125,000</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>¥150,000</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>¥175,000</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>¥200,000</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>¥225,000</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>¥250,000</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>¥275,000</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>¥300,000</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>¥325,000</t>
         </is>
       </c>
     </row>
@@ -2404,65 +2335,65 @@
           <t>【原価】撮影プラン (53%)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>¥40,000</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>¥80,000</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>¥120,000</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>¥120,000</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>¥160,000</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>¥160,000</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>¥200,000</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>¥200,000</t>
-        </is>
-      </c>
-      <c r="M14" s="12" t="inlineStr">
-        <is>
-          <t>¥240,000</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>¥240,000</t>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>¥79,500</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>¥159,000</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>¥238,500</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>¥238,500</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>¥318,000</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>¥318,000</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>¥397,500</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>¥397,500</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>¥477,000</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>¥477,000</t>
         </is>
       </c>
     </row>
@@ -2472,473 +2403,541 @@
           <t>【原価】月額掲載 (10%)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr"/>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>¥3,000</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>¥9,000</t>
         </is>
       </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>¥18,000</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>¥15,000</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>¥24,000</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t>¥27,000</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>¥30,000</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr">
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>¥36,000</t>
         </is>
       </c>
-      <c r="N15" s="12" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>¥39,000</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>¥45,000</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>¥51,000</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>【原価】成果報酬 (2%)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>¥18,000</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>¥36,000</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>¥36,000</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>¥54,000</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>¥54,000</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>¥72,000</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>¥72,000</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>¥90,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>【原価】SaaS (16%)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr"/>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>¥12,000</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>¥24,000</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>¥36,000</t>
-        </is>
-      </c>
-      <c r="M16" s="12" t="inlineStr">
-        <is>
-          <t>¥48,000</t>
-        </is>
-      </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>¥60,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>¥16,000</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>¥32,000</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>¥72,000</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>¥88,000</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>¥128,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>変動原価 合計</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>¥7,500</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>¥55,000</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>¥100,000</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>¥150,500</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>¥161,500</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>¥218,000</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
-        <is>
-          <t>¥243,500</t>
-        </is>
-      </c>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>¥303,500</t>
-        </is>
-      </c>
-      <c r="L17" s="14" t="inlineStr">
-        <is>
-          <t>¥326,000</t>
-        </is>
-      </c>
-      <c r="M17" s="14" t="inlineStr">
-        <is>
-          <t>¥389,000</t>
-        </is>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
-        <is>
-          <t>¥409,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr"/>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>¥50,000</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>¥75,000</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>¥179,500</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>¥284,000</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>¥415,500</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>¥464,500</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>¥578,000</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>¥643,000</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>¥769,500</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>¥855,500</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>¥982,000</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>¥1,071,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>粗利</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr"/>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>¥167,500</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>¥270,000</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>¥350,000</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>¥579,500</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>¥678,500</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>¥962,000</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>¥1,246,500</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>¥1,416,500</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>¥1,674,000</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>¥1,971,000</t>
-        </is>
-      </c>
-      <c r="N19" s="16" t="inlineStr">
-        <is>
-          <t>¥2,106,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr"/>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>¥450,000</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>¥675,000</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>¥970,500</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>¥1,266,000</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>¥2,524,500</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>¥3,685,500</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>¥4,062,000</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>¥5,307,000</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>¥5,740,500</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>¥7,084,500</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>¥7,518,000</t>
+        </is>
+      </c>
+      <c r="N20" s="14" t="inlineStr">
+        <is>
+          <t>¥8,889,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>粗利率</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr"/>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr"/>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="K20" s="18" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="L20" s="18" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="N20" s="18" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>固定費 (人件費・家賃・SaaS)</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="I22" s="20" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="J22" s="20" t="inlineStr">
+      <c r="J23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="K22" s="20" t="inlineStr">
+      <c r="K23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="L22" s="20" t="inlineStr">
+      <c r="L23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="M22" s="20" t="inlineStr">
+      <c r="M23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
-      <c r="N22" s="20" t="inlineStr">
+      <c r="N23" s="18" t="inlineStr">
         <is>
           <t>¥600,000</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr"/>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>¥-600,000</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>¥-432,500</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>¥-330,000</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>¥-250,000</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
-        <is>
-          <t>¥-20,500</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
-        <is>
-          <t>¥78,500</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>¥362,000</t>
-        </is>
-      </c>
-      <c r="J23" s="22" t="inlineStr">
-        <is>
-          <t>¥646,500</t>
-        </is>
-      </c>
-      <c r="K23" s="22" t="inlineStr">
-        <is>
-          <t>¥816,500</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="inlineStr">
-        <is>
-          <t>¥1,074,000</t>
-        </is>
-      </c>
-      <c r="M23" s="22" t="inlineStr">
-        <is>
-          <t>¥1,371,000</t>
-        </is>
-      </c>
-      <c r="N23" s="22" t="inlineStr">
-        <is>
-          <t>¥1,506,000</t>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>¥-150,000</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>¥75,000</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>¥370,500</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>¥666,000</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>¥1,924,500</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>¥3,085,500</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>¥3,462,000</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>¥4,707,000</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>¥5,140,500</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>¥6,484,500</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
+        <is>
+          <t>¥6,918,000</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>¥8,289,000</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2970,7 +2969,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>④ プラン別 原価・粗利</t>
+          <t>④ プラン別 原価・粗利 (全員同一)</t>
         </is>
       </c>
     </row>
@@ -3009,314 +3008,198 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>見学会予約 (1件)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>¥50,000</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>¥5,000</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>¥45,000</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>見学会予約 (10社半額)</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>¥25,000</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>¥5,000</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>撮影プラン (1本)</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>¥150,000</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>¥80,000</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>¥70,000</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>月額ベーシック (1社/月)</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>¥30,000</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>¥3,000</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>¥27,000</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>月額プロ (1社/月)</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>¥80,000</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>¥10,000</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>¥70,000</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>成果報酬 (¥3000万契約想定)</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>¥900,000</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>¥20,000</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>¥880,000</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>SaaS ライト (1社/月)</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>¥50,000</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>¥8,000</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>¥42,000</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>SaaS プロ (1社/月)</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>¥150,000</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>¥30,000</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>¥120,000</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>成果報酬 (¥3000万契約想定)</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>¥900,000</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>¥20,000</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>¥880,000</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>撮影プラン (1本)</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>¥150,000</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>¥80,000</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>¥70,000</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>撮影プラン (10社半額)</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>¥75,000</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>¥80,000</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>¥-5,000</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>−7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>月額ベーシック</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>¥30,000</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>¥3,000</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>¥27,000</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>月額ベーシック (10社半額)</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>¥15,000</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>¥3,000</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>¥12,000</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>月額プロ</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>¥80,000</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>¥10,000</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>¥70,000</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>SaaS ライト</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>¥50,000</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>¥8,000</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>¥42,000</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>SaaS ライト (10社半額)</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>¥25,000</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>¥8,000</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>¥17,000</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>SaaS プロ</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>¥150,000</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>¥30,000</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>¥120,000</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>※ 10社優遇の撮影プラン (¥75,000/本) は原価割れの可能性あり。Phase 2 入ったら撮影コストの削減交渉が必要。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3328,7 +3211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3413,7 +3296,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Phase 2 から業務委託1名想定</t>
+          <t>Phase 2から業務委託1名想定</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3340,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Phase 1 は Hobby で OK、Phase 2 から Pro</t>
+          <t>Phase 1 は Hobby</t>
         </is>
       </c>
     </row>
@@ -3499,110 +3382,102 @@
           <t>¥36,000</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Phase 1 から</t>
-        </is>
-      </c>
+      <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>GA4 / Search Console</t>
+          <t>ドメイン</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>¥0</t>
+          <t>¥1,500</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>¥0</t>
+          <t>¥18,000</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>無料</t>
+          <t>payhome.jp</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>ドメイン</t>
+          <t>経理ソフト (freee)</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>¥1,500</t>
+          <t>¥3,000</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>¥18,000</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>payhome.jp</t>
-        </is>
-      </c>
+          <t>¥36,000</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>経理ソフト (freee)</t>
+          <t>オフィス家賃</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>¥3,000</t>
+          <t>¥80,000</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>¥36,000</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
+          <t>¥960,000</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>鹿児島拠点</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>オフィス家賃</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>¥80,000</t>
+          <t>¥10,000</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>¥960,000</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>鹿児島拠点</t>
-        </is>
-      </c>
+          <t>¥120,000</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>水道光熱費</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>¥10,000</t>
+          <t>¥15,000</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>¥120,000</t>
+          <t>¥180,000</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -3610,82 +3485,64 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>水道光熱費</t>
+          <t>交通費</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>¥15,000</t>
+          <t>¥20,000</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>¥180,000</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
+          <t>¥240,000</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>工務店訪問</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>交通費</t>
+          <t>広告宣伝費</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>¥20,000</t>
+          <t>¥10,000</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>¥240,000</t>
+          <t>¥120,000</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>工務店訪問</t>
+          <t>Phase 1 は YouTube オーガニック</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>広告宣伝費</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>¥10,000</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>¥120,000</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Phase 1 は YouTube のオーガニックで</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>¥599,500</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>¥7,194,000</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr"/>
+      <c r="D18" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3748,220 +3605,220 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>前月末</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>月次請求台帳 (①シート) に当月発生する請求を記入</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>月初3営業日以内</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>請求書テンプレートで各社の請求書を作成</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>月初3営業日以内</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>請求書を PDF で工務店様へメール送信</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>送信当日</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>入金管理シート (②) に請求行を追加</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>月末</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>入金確認 → 入金管理シートを更新</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>月末翌日</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>未入金案件を PM へエスカレーション</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>月末</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>月次P&amp;L シート (③) を実績値で更新</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>月末翌日</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>代表・経理へ月次レポート共有</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>四半期ごと</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>代表・経理</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>消費税・法人税の納付準備</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>年度末</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>代表・経理</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>決算書作成 (外部税理士に依頼)</t>
         </is>
